--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar-new/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34CAF33-7171-394E-AADB-BD85C152020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8C4C2C-A28D-8540-8107-CB61386FF855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <t>robotics;ai</t>
   </si>
   <si>
-    <t>assets/images/publications/JHockey.jpg</t>
-  </si>
-  <si>
     <t>Two mechatronic robots fighting for a hockey puck in an arena.</t>
   </si>
   <si>
@@ -298,6 +295,9 @@
   </si>
   <si>
     <t>Pneumatactors: Soft interface for co-located multimodal tactile stimuli.</t>
+  </si>
+  <si>
+    <t>assets/images/publications/JHockey.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1422,7 @@
         <v>67</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>57</v>
@@ -1473,13 +1473,13 @@
     </row>
     <row r="7" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>43</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:12" ht="95" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="76" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>46</v>
       </c>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="171" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="152" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>61</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>65</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
@@ -1628,10 +1628,10 @@
         <v>2024</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>70</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8C4C2C-A28D-8540-8107-CB61386FF855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1E00B9-D3A9-2B43-9806-358C66029EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -80,9 +80,6 @@
     <t>British Journal of Anaesthesia</t>
   </si>
   <si>
-    <t>assets/images/publications/ECGRiskStratification.png</t>
-  </si>
-  <si>
     <t>Robert Stevens observes an electrocardiogram monitor</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>IEEE Sensors Letters</t>
   </si>
   <si>
-    <t>assets/images/publications/FirstContactStiffnessEstimation.png</t>
-  </si>
-  <si>
     <t>Prosthetic hand with tactile sensor</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>IEEE International Conference on Neural Engineering</t>
   </si>
   <si>
-    <t>assets/images/publications/Placeholder.png</t>
-  </si>
-  <si>
     <t>Optimizing cross-modal matching for multimodal motor rehabilitation.</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
     <t>International Conference on Rehabilitation Robotics</t>
   </si>
   <si>
-    <t>assets/images/publications/CrossModalMatching.mp4</t>
-  </si>
-  <si>
     <t>Visual-haptic feedback enhances finger individuation in a virtual precision grip neurotraining task.</t>
   </si>
   <si>
@@ -158,18 +146,12 @@
     <t>Biomedical Engineering Society Annual Meeting</t>
   </si>
   <si>
-    <t>assets/images/publications/HANDDevice.png</t>
-  </si>
-  <si>
     <t>Pneumatactor arrays for high frequency vibrotactile feedback.</t>
   </si>
   <si>
     <t>IEEE Haptics Symposium</t>
   </si>
   <si>
-    <t>assets/images/publications/Pneumatactors.png</t>
-  </si>
-  <si>
     <t>Paper|https://ieeexplore.ieee.org/document/10012345</t>
   </si>
   <si>
@@ -179,9 +161,6 @@
     <t>Anway Pimpalkar; Rashmika Patole; Ketaki Kamble; Mahesh H. Shindikar</t>
   </si>
   <si>
-    <t>assets/images/publications/SkullStripping.png</t>
-  </si>
-  <si>
     <t>In neuroimaging, skull stripping is vital for removing non-brain tissue from scans, improving accuracy in analysis, segmentation, and 3D modeling. While traditional methods are dependable, they struggle large, multi-scanner datasets. Deep learning, powered by U-Net architectures, provides a faster, more efficient solution, robust against multi-scanner variability.</t>
   </si>
   <si>
@@ -215,9 +194,6 @@
     <t>We are designing an experiment to explore how different forms of feedback — visual, haptic, and combined — affect motor performance in a precision grip task. Participants used isometric force to “pinch” virtual objects while receiving real-time feedback through either vision, vibration, or both. The study showed that while visual feedback alone often led to high success rates, combining it haptic feedback offered perceptual and learning benefits in specific contexts. These findings underscore the importance of tailoring multimodal feedback to user needs and task demands, especially in the design of next-generation rehabilitation tools for stroke recovery and sensorimotor training.</t>
   </si>
   <si>
-    <t>assets/images/publications/ProspectiveSenseOfAgency.png</t>
-  </si>
-  <si>
     <t>Automating wild blueberry harvesters to reduce operator load and improve yield.</t>
   </si>
   <si>
@@ -228,9 +204,6 @@
   </si>
   <si>
     <t>Dalhousie University, Canada</t>
-  </si>
-  <si>
-    <t>assets/images/publications/BlueberryHarvesting.jpg</t>
   </si>
   <si>
     <t>robotics;</t>
@@ -297,7 +270,34 @@
     <t>Pneumatactors: Soft interface for co-located multimodal tactile stimuli.</t>
   </si>
   <si>
-    <t>assets/images/publications/JHockey.jpeg</t>
+    <t>/assets/images/publications/ECGRiskStratification.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/FirstContactStiffnessEstimation.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/Placeholder.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/CrossModalMatching.mp4</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/HANDDevice.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/Pneumatactors.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/SkullStripping.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/ProspectiveSenseOfAgency.png</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/BlueberryHarvesting.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/JHockey.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="76" x14ac:dyDescent="0.25">
@@ -1312,317 +1312,317 @@
         <v>2025</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="95" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="6">
         <v>2025</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="K3" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="228" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="E4" s="8">
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" ht="171" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="6">
         <v>2025</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="152" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <v>2024</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E7" s="8">
         <v>2024</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:12" ht="76" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="95" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E8" s="8">
         <v>2023</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="133" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8">
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="152" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="171" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E10" s="8">
         <v>2022</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E11" s="8">
         <v>2024</v>
@@ -1631,17 +1631,17 @@
         <v>86</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L11" s="9"/>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1E00B9-D3A9-2B43-9806-358C66029EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E343BAD7-0B36-2544-A91B-6BA72A5D1D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -276,15 +276,9 @@
     <t>/assets/images/publications/FirstContactStiffnessEstimation.png</t>
   </si>
   <si>
-    <t>/assets/images/publications/Placeholder.png</t>
-  </si>
-  <si>
     <t>/assets/images/publications/CrossModalMatching.mp4</t>
   </si>
   <si>
-    <t>/assets/images/publications/HANDDevice.png</t>
-  </si>
-  <si>
     <t>/assets/images/publications/Pneumatactors.png</t>
   </si>
   <si>
@@ -298,6 +292,12 @@
   </si>
   <si>
     <t>/assets/images/publications/JHockey.jpeg</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/HANDDevice.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/SenseMatch.jpg</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1384,7 @@
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -1416,7 +1416,7 @@
         <v>2025</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>58</v>
@@ -1454,7 +1454,7 @@
         <v>2024</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>59</v>
@@ -1488,7 +1488,7 @@
         <v>2024</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>37</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:12" ht="95" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="76" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>2023</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>40</v>
@@ -1558,7 +1558,7 @@
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>44</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="171" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="152" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>2022</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>73</v>
@@ -1628,7 +1628,7 @@
         <v>2024</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>72</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E343BAD7-0B36-2544-A91B-6BA72A5D1D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30227B52-6A13-1645-A159-9FEA139597BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
@@ -224,11 +224,6 @@
     <t>530.421 Mechatronics Course, with Jeremy D. Brown</t>
   </si>
   <si>
-    <t>Wild blueberries, loved for their bold flavors, grow close to the ground in rocky terrains, posing challenges for automated harvesting setups. To address this, I aided in the development of automated harvester-head height adjusting, and a camera-vision-based system to automate berry volume measurement and bin switching to reduce operator workload.
-&lt;br /&gt;&lt;br /&gt;
-This project was funded by &lt;a class="link" href="https://www.mitacs.ca/our-programs/globalink-research-internship-students/" target="_blank"&gt;Mitacs Globalink&lt;/a&gt;, a prestigious program supporting top undergraduates from 17 countries for fully funded summer research in Canada.</t>
-  </si>
-  <si>
     <t>JHockey: Communication platform for multi-robots playing hockey.</t>
   </si>
   <si>
@@ -298,6 +293,11 @@
   </si>
   <si>
     <t>/assets/images/publications/SenseMatch.jpg</t>
+  </si>
+  <si>
+    <t>Wild blueberries, loved for their bold flavors, grow close to the ground in rocky terrains, posing challenges for automated harvesting setups. To address this, I aided in the development of automated harvester-head height adjusting, and a camera-vision-based system to automate berry volume measurement and bin switching to reduce operator workload.
+&lt;br /&gt;&lt;br /&gt;
+This project was funded by &lt;a class="link" href="https://www.mitacs.ca/our-programs/globalink-research-internship-students/" target="_blank"&gt;Mitacs Globalink&lt;/a&gt;, a program supporting top undergraduates from 17 countries for fully funded summer research in Canada.</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="76" x14ac:dyDescent="0.25">
@@ -1312,7 +1312,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>15</v>
@@ -1348,7 +1348,7 @@
         <v>2025</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>22</v>
@@ -1363,7 +1363,7 @@
         <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L3" s="7"/>
     </row>
@@ -1384,12 +1384,12 @@
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>25</v>
@@ -1416,13 +1416,13 @@
         <v>2025</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>58</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>50</v>
@@ -1434,7 +1434,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="152" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>2024</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>59</v>
@@ -1473,13 +1473,13 @@
     </row>
     <row r="7" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>38</v>
@@ -1488,7 +1488,7 @@
         <v>2024</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>37</v>
@@ -1520,7 +1520,7 @@
         <v>2023</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>40</v>
@@ -1538,7 +1538,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="133" x14ac:dyDescent="0.25">
@@ -1558,14 +1558,14 @@
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>46</v>
@@ -1592,14 +1592,14 @@
         <v>2022</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>46</v>
@@ -1608,12 +1608,12 @@
         <v>57</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>48</v>
@@ -1628,10 +1628,10 @@
         <v>2024</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>61</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30227B52-6A13-1645-A159-9FEA139597BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F176022-B4E9-1940-B79D-174135AA0341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>section</t>
   </si>
@@ -113,9 +113,6 @@
     <t>graduate research</t>
   </si>
   <si>
-    <t>robotics;neuro</t>
-  </si>
-  <si>
     <t>In Conferences</t>
   </si>
   <si>
@@ -125,27 +122,18 @@
     <t>A. Michael West Jr.; Anway Pimpalkar; Jing Xu; Jeremy D. Brown</t>
   </si>
   <si>
-    <t>IEEE International Conference on Neural Engineering</t>
-  </si>
-  <si>
     <t>Optimizing cross-modal matching for multimodal motor rehabilitation.</t>
   </si>
   <si>
     <t>Anway Pimpalkar; A. Michael West Jr.; Jing Xu; Jeremy D. Brown</t>
   </si>
   <si>
-    <t>International Conference on Rehabilitation Robotics</t>
-  </si>
-  <si>
     <t>Visual-haptic feedback enhances finger individuation in a virtual precision grip neurotraining task.</t>
   </si>
   <si>
     <t>Anway Pimpalkar; Divya Rai; Uli Bartels; Jing Xu; Jeremy D. Brown</t>
   </si>
   <si>
-    <t>Biomedical Engineering Society Annual Meeting</t>
-  </si>
-  <si>
     <t>Pneumatactor arrays for high frequency vibrotactile feedback.</t>
   </si>
   <si>
@@ -174,9 +162,6 @@
   </si>
   <si>
     <t>internship</t>
-  </si>
-  <si>
-    <t>ai;neuro</t>
   </si>
   <si>
     <t>Teaching Tools</t>
@@ -265,9 +250,6 @@
     <t>Pneumatactors: Soft interface for co-located multimodal tactile stimuli.</t>
   </si>
   <si>
-    <t>/assets/images/publications/ECGRiskStratification.png</t>
-  </si>
-  <si>
     <t>/assets/images/publications/FirstContactStiffnessEstimation.png</t>
   </si>
   <si>
@@ -298,6 +280,41 @@
     <t>Wild blueberries, loved for their bold flavors, grow close to the ground in rocky terrains, posing challenges for automated harvesting setups. To address this, I aided in the development of automated harvester-head height adjusting, and a camera-vision-based system to automate berry volume measurement and bin switching to reduce operator workload.
 &lt;br /&gt;&lt;br /&gt;
 This project was funded by &lt;a class="link" href="https://www.mitacs.ca/our-programs/globalink-research-internship-students/" target="_blank"&gt;Mitacs Globalink&lt;/a&gt;, a program supporting top undergraduates from 17 countries for fully funded summer research in Canada.</t>
+  </si>
+  <si>
+    <t>robotics;HCI</t>
+  </si>
+  <si>
+    <t>ai;HCI</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/JHU_AI_ECG.jpeg</t>
+  </si>
+  <si>
+    <t>Cross-modal matching is not bidirectional: Implications for human multisensory feedback.</t>
+  </si>
+  <si>
+    <t>A. Michael West Jr.; Berk Kasimcan; Anway Pimpalkar; Jing Xu; Jeremy D. Brown</t>
+  </si>
+  <si>
+    <t>IEEE International Conference on Biomedical Robotics Biomechatronics (BioRob)</t>
+  </si>
+  <si>
+    <t>IEEE International Conference on Neural Engineering (NER)</t>
+  </si>
+  <si>
+    <t>International Conference on Rehabilitation Robotics (ICORR)</t>
+  </si>
+  <si>
+    <t>Biomedical Engineering Society Annual Meeting (BMES)</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/CrossModalMatching_BioRob.mp4</t>
+  </si>
+  <si>
+    <t>This work builds on another project, listed below, &lt;em&gt;"Optimizing cross-modal matching for multimodal motor rehabilitation."&lt;/em&gt;
+&lt;br /&gt;&lt;br /&gt;
+Cross-modal matching (CMM) is widely used to calibrate sensory feedback across modalities, but it is typically assumed to be bidirectional and invertible. We test this assumption using visual–vibrotactile and co-located haptic (pressure–vibration) datasets and show that it does not hold. At the individual level, mappings are systematically non-invertible, with directional asymmetries arising from structured, intensity-dependent distortions rather than noise. As a result, CMM compresses the perceptual range of one modality relative to another, making the choice of mapping direction consequential. These findings show that CMM is not a neutral calibration step but a directional design decision that shapes perception and learning in human–machine systems.</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36804C05-0050-DB4A-B44D-23DEA2DFD96A}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.5" style="1" customWidth="1"/>
@@ -1292,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="76" x14ac:dyDescent="0.25">
@@ -1312,7 +1329,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>15</v>
@@ -1348,7 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>22</v>
@@ -1363,287 +1380,319 @@
         <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="228" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E4" s="8">
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="L4" s="9"/>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" ht="171" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:12" s="3" customFormat="1" ht="228" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="8">
         <v>2025</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="F5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" s="3" customFormat="1" ht="171" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" ht="152" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E6" s="6">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="I6" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="152" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="7"/>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2024</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="38" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="8">
+    <row r="8" spans="1:12" ht="38" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="8">
         <v>2024</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" spans="1:12" ht="95" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12" ht="76" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2023</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="133" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="E9" s="8">
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="I9" s="8" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" ht="152" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="133" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E10" s="8">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" spans="1:12" ht="152" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2022</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="38" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="38" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="D12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="8">
         <v>2024</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" s="9"/>
+      <c r="F12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F176022-B4E9-1940-B79D-174135AA0341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BECF8-A5EC-E048-BAB3-3E859A4C4475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
@@ -152,9 +152,6 @@
     <t>In neuroimaging, skull stripping is vital for removing non-brain tissue from scans, improving accuracy in analysis, segmentation, and 3D modeling. While traditional methods are dependable, they struggle large, multi-scanner datasets. Deep learning, powered by U-Net architectures, provides a faster, more efficient solution, robust against multi-scanner variability.</t>
   </si>
   <si>
-    <t>Internships</t>
-  </si>
-  <si>
     <t>Elucidating the electrophysiological correlates of prospective sense of agency.</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
   </si>
   <si>
     <t>internship</t>
-  </si>
-  <si>
-    <t>Teaching Tools</t>
   </si>
   <si>
     <t>teaching</t>
@@ -315,6 +309,12 @@
     <t>This work builds on another project, listed below, &lt;em&gt;"Optimizing cross-modal matching for multimodal motor rehabilitation."&lt;/em&gt;
 &lt;br /&gt;&lt;br /&gt;
 Cross-modal matching (CMM) is widely used to calibrate sensory feedback across modalities, but it is typically assumed to be bidirectional and invertible. We test this assumption using visual–vibrotactile and co-located haptic (pressure–vibration) datasets and show that it does not hold. At the individual level, mappings are systematically non-invertible, with directional asymmetries arising from structured, intensity-dependent distortions rather than noise. As a result, CMM compresses the perceptual range of one modality relative to another, making the choice of mapping direction consequential. These findings show that CMM is not a neutral calibration step but a directional design decision that shapes perception and learning in human–machine systems.</t>
+  </si>
+  <si>
+    <t>At Internships</t>
+  </si>
+  <si>
+    <t>In Class (Teaching Tools)</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="76" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>15</v>
@@ -1365,7 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>22</v>
@@ -1380,39 +1380,39 @@
         <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="228" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" s="8">
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L4" s="9"/>
     </row>
@@ -1427,24 +1427,24 @@
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" s="8">
         <v>2025</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L5" s="9"/>
     </row>
@@ -1459,31 +1459,31 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" s="6">
         <v>2025</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="152" x14ac:dyDescent="0.25">
@@ -1497,38 +1497,38 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" s="6">
         <v>2024</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>34</v>
@@ -1537,7 +1537,7 @@
         <v>2024</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>33</v>
@@ -1548,11 +1548,11 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:12" ht="95" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="76" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>36</v>
       </c>
@@ -1563,13 +1563,13 @@
         <v>37</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" s="8">
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>36</v>
@@ -1581,116 +1581,116 @@
         <v>38</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="133" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="E10" s="8">
         <v>2023</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="152" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8">
         <v>2022</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" s="8">
         <v>2024</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L12" s="9"/>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BECF8-A5EC-E048-BAB3-3E859A4C4475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959EED41-2FFD-4142-AE60-AEF58A605FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
   <si>
     <t>section</t>
   </si>
@@ -294,9 +294,6 @@
     <t>IEEE International Conference on Biomedical Robotics Biomechatronics (BioRob)</t>
   </si>
   <si>
-    <t>IEEE International Conference on Neural Engineering (NER)</t>
-  </si>
-  <si>
     <t>International Conference on Rehabilitation Robotics (ICORR)</t>
   </si>
   <si>
@@ -315,6 +312,12 @@
   </si>
   <si>
     <t>In Class (Teaching Tools)</t>
+  </si>
+  <si>
+    <t>Paper|https://ieeexplore.ieee.org/document/11589033</t>
+  </si>
+  <si>
+    <t>IEEE EMBS Conference on Neural Engineering (NER)</t>
   </si>
 </sst>
 </file>
@@ -1401,12 +1404,12 @@
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>25</v>
@@ -1427,7 +1430,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E5" s="8">
         <v>2025</v>
@@ -1436,7 +1439,9 @@
         <v>77</v>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="I5" s="8" t="s">
         <v>58</v>
       </c>
@@ -1459,7 +1464,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" s="6">
         <v>2025</v>
@@ -1497,7 +1502,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" s="6">
         <v>2024</v>
@@ -1595,7 +1600,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>47</v>
@@ -1629,7 +1634,7 @@
         <v>46</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>48</v>
@@ -1665,7 +1670,7 @@
         <v>56</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>55</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959EED41-2FFD-4142-AE60-AEF58A605FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B937BD11-19F6-5841-9156-4CEAAE1E1F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B937BD11-19F6-5841-9156-4CEAAE1E1F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC637301-E9E1-CD48-AE64-936D347E5C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="-38400" yWindow="-1960" windowWidth="38400" windowHeight="21600" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="99">
   <si>
     <t>section</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>IEEE Haptics Symposium</t>
-  </si>
-  <si>
-    <t>Paper|https://ieeexplore.ieee.org/document/10012345</t>
   </si>
   <si>
     <t>Performance evaluation of vanilla, residual, and dense 2D U-Net architectures for skull stripping of augmented 3D T1-weighted MRI head scans.</t>
@@ -318,6 +315,27 @@
   </si>
   <si>
     <t>IEEE EMBS Conference on Neural Engineering (NER)</t>
+  </si>
+  <si>
+    <t>Paper|https://link.springer.com/chapter/10.1007/978-3-031-54547-4_11</t>
+  </si>
+  <si>
+    <t>Harvard University</t>
+  </si>
+  <si>
+    <t>GitHub|https://github.com/anwaypimpalkar/BE124-Labs</t>
+  </si>
+  <si>
+    <t>/assets/images/publications/BiomotumSpark.png</t>
+  </si>
+  <si>
+    <t>BE 124 Biomechanics and Assistive Robotics Course, with Patrick Slade</t>
+  </si>
+  <si>
+    <t>Biomotum ankle exoskeleton.</t>
+  </si>
+  <si>
+    <t>Exoskeleton interfacing and control teaching labs with the Biomotum SPARK.</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36804C05-0050-DB4A-B44D-23DEA2DFD96A}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.5" style="1" customWidth="1"/>
@@ -1312,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="76" x14ac:dyDescent="0.25">
@@ -1332,7 +1350,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>15</v>
@@ -1368,7 +1386,7 @@
         <v>2025</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>22</v>
@@ -1383,39 +1401,39 @@
         <v>25</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="228" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="E4" s="8">
         <v>2025</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L4" s="9"/>
     </row>
@@ -1430,26 +1448,26 @@
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" s="8">
         <v>2025</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L5" s="9"/>
     </row>
@@ -1464,31 +1482,31 @@
         <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" s="6">
         <v>2025</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="152" x14ac:dyDescent="0.25">
@@ -1502,38 +1520,38 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="6">
         <v>2024</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>34</v>
@@ -1542,7 +1560,7 @@
         <v>2024</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>33</v>
@@ -1553,151 +1571,185 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:12" ht="76" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="95" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="8">
         <v>2023</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="133" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="E10" s="8">
         <v>2023</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="152" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="E11" s="8">
         <v>2022</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="38" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E12" s="8">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="1:12" ht="38" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
